--- a/artfynd/A 33278-2022 artfynd.xlsx
+++ b/artfynd/A 33278-2022 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126111740</v>
+        <v>126112227</v>
       </c>
       <c r="B3" t="n">
         <v>57651</v>
@@ -806,21 +806,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564248</v>
+        <v>564238</v>
       </c>
       <c r="R3" t="n">
-        <v>6995730</v>
+        <v>6995665</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126112227</v>
+        <v>126111740</v>
       </c>
       <c r="B4" t="n">
         <v>57651</v>
@@ -913,16 +908,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564238</v>
+        <v>564248</v>
       </c>
       <c r="R4" t="n">
-        <v>6995665</v>
+        <v>6995730</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 33278-2022 artfynd.xlsx
+++ b/artfynd/A 33278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112218</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126112227</v>
+        <v>126111740</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,16 +806,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564238</v>
+        <v>564248</v>
       </c>
       <c r="R3" t="n">
-        <v>6995665</v>
+        <v>6995730</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126111740</v>
+        <v>126112227</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +913,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564248</v>
+        <v>564238</v>
       </c>
       <c r="R4" t="n">
-        <v>6995730</v>
+        <v>6995665</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,7 +989,7 @@
         <v>126111798</v>
       </c>
       <c r="B5" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>126111717</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>126111552</v>
       </c>
       <c r="B7" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33278-2022 artfynd.xlsx
+++ b/artfynd/A 33278-2022 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>126111798</v>
       </c>
       <c r="B5" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>126111552</v>
       </c>
       <c r="B7" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33278-2022 artfynd.xlsx
+++ b/artfynd/A 33278-2022 artfynd.xlsx
@@ -1083,50 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126111717</v>
+        <v>126111552</v>
       </c>
       <c r="B6" t="n">
-        <v>57652</v>
+        <v>98343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564216</v>
+        <v>564258</v>
       </c>
       <c r="R6" t="n">
-        <v>6995698</v>
+        <v>6995717</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1159,11 +1154,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,45 +1180,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126111552</v>
+        <v>126111717</v>
       </c>
       <c r="B7" t="n">
-        <v>98343</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564258</v>
+        <v>564216</v>
       </c>
       <c r="R7" t="n">
-        <v>6995717</v>
+        <v>6995698</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1261,6 +1256,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 33278-2022 artfynd.xlsx
+++ b/artfynd/A 33278-2022 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126111740</v>
+        <v>126112227</v>
       </c>
       <c r="B3" t="n">
         <v>57652</v>
@@ -806,21 +806,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564248</v>
+        <v>564238</v>
       </c>
       <c r="R3" t="n">
-        <v>6995730</v>
+        <v>6995665</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126112227</v>
+        <v>126111740</v>
       </c>
       <c r="B4" t="n">
         <v>57652</v>
@@ -913,16 +908,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564238</v>
+        <v>564248</v>
       </c>
       <c r="R4" t="n">
-        <v>6995665</v>
+        <v>6995730</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,7 +989,7 @@
         <v>126111798</v>
       </c>
       <c r="B5" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>126111552</v>
       </c>
       <c r="B6" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33278-2022 artfynd.xlsx
+++ b/artfynd/A 33278-2022 artfynd.xlsx
@@ -1083,45 +1083,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126111552</v>
+        <v>126111717</v>
       </c>
       <c r="B6" t="n">
-        <v>98345</v>
+        <v>57652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564258</v>
+        <v>564216</v>
       </c>
       <c r="R6" t="n">
-        <v>6995717</v>
+        <v>6995698</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1154,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,50 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126111717</v>
+        <v>126111552</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>98345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564216</v>
+        <v>564258</v>
       </c>
       <c r="R7" t="n">
-        <v>6995698</v>
+        <v>6995717</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1256,11 +1261,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 33278-2022 artfynd.xlsx
+++ b/artfynd/A 33278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112218</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126112227</v>
+        <v>126111740</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,16 +806,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564238</v>
+        <v>564248</v>
       </c>
       <c r="R3" t="n">
-        <v>6995665</v>
+        <v>6995730</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126111740</v>
+        <v>126112227</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +913,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564248</v>
+        <v>564238</v>
       </c>
       <c r="R4" t="n">
-        <v>6995730</v>
+        <v>6995665</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,7 +989,7 @@
         <v>126111798</v>
       </c>
       <c r="B5" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>126111717</v>
       </c>
       <c r="B6" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>126111552</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33278-2022 artfynd.xlsx
+++ b/artfynd/A 33278-2022 artfynd.xlsx
@@ -1193,7 +1193,7 @@
         <v>126111552</v>
       </c>
       <c r="B7" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33278-2022 artfynd.xlsx
+++ b/artfynd/A 33278-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126112218</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126111740</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>126112227</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>126111798</v>
       </c>
       <c r="B5" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>126111717</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>126111552</v>
       </c>
       <c r="B7" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33278-2022 artfynd.xlsx
+++ b/artfynd/A 33278-2022 artfynd.xlsx
@@ -1083,50 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126111717</v>
+        <v>126111552</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>98361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564216</v>
+        <v>564258</v>
       </c>
       <c r="R6" t="n">
-        <v>6995698</v>
+        <v>6995717</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1159,11 +1154,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,45 +1180,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126111552</v>
+        <v>126111717</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564258</v>
+        <v>564216</v>
       </c>
       <c r="R7" t="n">
-        <v>6995717</v>
+        <v>6995698</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1261,6 +1256,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 33278-2022 artfynd.xlsx
+++ b/artfynd/A 33278-2022 artfynd.xlsx
@@ -1083,45 +1083,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126111552</v>
+        <v>126111717</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564258</v>
+        <v>564216</v>
       </c>
       <c r="R6" t="n">
-        <v>6995717</v>
+        <v>6995698</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1154,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,50 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126111717</v>
+        <v>126111552</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>98361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564216</v>
+        <v>564258</v>
       </c>
       <c r="R7" t="n">
-        <v>6995698</v>
+        <v>6995717</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1256,11 +1261,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 33278-2022 artfynd.xlsx
+++ b/artfynd/A 33278-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126112218</v>
+        <v>126111798</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammelbodbäcken, Jmt</t>
+          <t>Bodkyrkan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564253</v>
+        <v>564390</v>
       </c>
       <c r="R2" t="n">
-        <v>6995642</v>
+        <v>6995589</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126111740</v>
+        <v>126111717</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564248</v>
+        <v>564216</v>
       </c>
       <c r="R3" t="n">
-        <v>6995730</v>
+        <v>6995698</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126112227</v>
+        <v>126111740</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,16 +908,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564238</v>
+        <v>564248</v>
       </c>
       <c r="R4" t="n">
-        <v>6995665</v>
+        <v>6995730</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126111798</v>
+        <v>126112218</v>
       </c>
       <c r="B5" t="n">
-        <v>91245</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,37 +997,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodkyrkan, Jmt</t>
+          <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564390</v>
+        <v>564253</v>
       </c>
       <c r="R5" t="n">
-        <v>6995589</v>
+        <v>6995642</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126111717</v>
+        <v>126112227</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1117,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelbodbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564216</v>
+        <v>564238</v>
       </c>
       <c r="R6" t="n">
-        <v>6995698</v>
+        <v>6995665</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,7 +1193,7 @@
         <v>126111552</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33278-2022 artfynd.xlsx
+++ b/artfynd/A 33278-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126111798</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126111717</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126111740</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126112218</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126112227</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,8 +1314,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126111552</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>